--- a/data/department_schedules_finals/Jeoloji Mühendisliği.xlsx
+++ b/data/department_schedules_finals/Jeoloji Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\modified\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE9052E-1FE7-47E6-BBF5-1371F18BF230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{3BE9052E-1FE7-47E6-BBF5-1371F18BF230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A88F44D3-A294-408B-8727-C1DCD38C0A26}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>Year:</t>
   </si>
@@ -176,6 +176,18 @@
   </si>
   <si>
     <t>Rooms Used</t>
+  </si>
+  <si>
+    <t>C205</t>
+  </si>
+  <si>
+    <t>CAD1</t>
+  </si>
+  <si>
+    <t>C203,C209,C213</t>
+  </si>
+  <si>
+    <t>C202</t>
   </si>
 </sst>
 </file>
@@ -282,6 +294,38 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -310,38 +354,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -356,15 +368,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}" name="Table1" displayName="Table1" ref="A1:F24" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}" name="Table1" displayName="Table1" ref="A1:F24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F24" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9AA74D43-5C0D-4306-BA2C-33CA0D410808}" name="Year:" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{F7E028DF-0DCD-415A-98CA-91B412F89F36}" name="Course ID" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{8C05F5BE-9786-4856-B842-56932FB33F47}" name="Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{152198DF-19A4-4BC8-9C22-22E53A138922}" name="Rooms" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{F0A321C5-0531-4413-A331-945817A1B833}" name="Course Name" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{4F78AD98-4FF1-4478-9539-6BE250A65DF9}" name="Rooms Used" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{9AA74D43-5C0D-4306-BA2C-33CA0D410808}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{F7E028DF-0DCD-415A-98CA-91B412F89F36}" name="Course ID" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{8C05F5BE-9786-4856-B842-56932FB33F47}" name="Date" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{152198DF-19A4-4BC8-9C22-22E53A138922}" name="Rooms" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{F0A321C5-0531-4413-A331-945817A1B833}" name="Course Name" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{4F78AD98-4FF1-4478-9539-6BE250A65DF9}" name="Rooms Used" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -658,14 +670,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="33.26953125" customWidth="1"/>
-    <col min="6" max="6" width="42.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="33.265625" customWidth="1"/>
+    <col min="6" max="6" width="42.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,7 +697,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -701,9 +713,11 @@
       <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -719,9 +733,11 @@
       <c r="E3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -737,9 +753,11 @@
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -755,9 +773,11 @@
       <c r="E5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -773,9 +793,11 @@
       <c r="E6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -791,9 +813,11 @@
       <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -809,9 +833,11 @@
       <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -827,9 +853,11 @@
       <c r="E9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -845,9 +873,11 @@
       <c r="E10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -863,9 +893,11 @@
       <c r="E11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -881,9 +913,11 @@
       <c r="E12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -899,9 +933,11 @@
       <c r="E13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F13" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -917,9 +953,11 @@
       <c r="E14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F14" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -935,9 +973,11 @@
       <c r="E15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F15" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -953,9 +993,11 @@
       <c r="E16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F16" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -971,9 +1013,11 @@
       <c r="E17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F17" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -989,9 +1033,11 @@
       <c r="E18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1007,9 +1053,11 @@
       <c r="E19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <v>4</v>
       </c>
@@ -1025,9 +1073,11 @@
       <c r="E20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F20" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>4</v>
       </c>
@@ -1043,9 +1093,11 @@
       <c r="E21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -1061,9 +1113,11 @@
       <c r="E22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1079,9 +1133,11 @@
       <c r="E23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1097,7 +1153,9 @@
       <c r="E24" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
